--- a/data/trans_bre/P1801_2016_2023-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1801_2016_2023-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 17,44</t>
+          <t>6,25; 17,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 9,99</t>
+          <t>0,44; 10,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 37,39</t>
+          <t>12,01; 37,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 20,75</t>
+          <t>0,87; 22,0</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,49%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 16,1</t>
+          <t>7,31; 16,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 9,6</t>
+          <t>5,19; 14,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,18; 38,63</t>
+          <t>15,58; 38,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 19,26</t>
+          <t>10,1; 30,44</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,86</t>
+          <t>8,85</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 18,92</t>
+          <t>8,5; 18,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 39,16</t>
+          <t>4,24; 14,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,31; 43,25</t>
+          <t>17,19; 42,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 98,84</t>
+          <t>10,06; 38,64</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 10,72</t>
+          <t>1,94; 11,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 8,75</t>
+          <t>2,64; 11,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 24,21</t>
+          <t>3,85; 25,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 17,26</t>
+          <t>4,98; 23,18</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 13,09</t>
+          <t>8,06; 13,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 11,92</t>
+          <t>5,59; 10,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,08; 28,89</t>
+          <t>16,93; 29,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 23,45</t>
+          <t>11,42; 22,67</t>
         </is>
       </c>
     </row>
